--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
   <si>
     <t>48965</t>
   </si>
@@ -158,7 +158,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -167,28 +167,22 @@
     <t>Departamento de contabilidad</t>
   </si>
   <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
     <t>05/04/2018</t>
   </si>
   <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>2B39D995838641426B2DF9A2D2E7ABBA</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de abril de 2022 al 30 de junio de 2022,  el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos y a las personas físicas o morales que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier otro motivo, apegándose únicamente a los conceptos establecidos en las Condiciones Generales de Trabajo y Contrato Colectivo de Trabajo, en este sentido al no existir información qué publicar, no se establece un hipervínculo de los programas con objetivos y metas.</t>
-  </si>
-  <si>
-    <t>536B85C7EAA2DBD90F2FE0E51AE34CE0</t>
-  </si>
-  <si>
-    <t>41A1DFAF229DB6683C255E6EB03CC50E</t>
+    <t>36158AC546A76EBD1E356BCA7C1EF726</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de abril de 2023 al 30 de junio de 2023,  el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier otro motivo, apegándose únicamente a los conceptos establecidos en las Condiciones Generales de Trabajo y Contrato Colectivo de Trabajo, en este sentido al no existir información qué publicar, no se ha modificado la fecha de actualización y en su caso establecer un hipervínculo de los programas con objetivos y metas.</t>
   </si>
   <si>
     <t>Efectivo</t>
@@ -590,10 +584,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -828,10 +822,10 @@
         <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>47</v>
@@ -864,118 +858,12 @@
         <v>48</v>
       </c>
       <c r="O8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="Q8" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q10" s="2" t="s">
         <v>54</v>
       </c>
     </row>
@@ -990,7 +878,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E192">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -1005,17 +893,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
